--- a/RaidenDemo/文档/配置表/__enums__.xlsx
+++ b/RaidenDemo/文档/配置表/__enums__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="220">
   <si>
     <t>##var</t>
   </si>
@@ -564,6 +564,129 @@
   </si>
   <si>
     <t>浮点数</t>
+  </si>
+  <si>
+    <t>StateValueType</t>
+  </si>
+  <si>
+    <t>状态值类型</t>
+  </si>
+  <si>
+    <t>当前生命</t>
+  </si>
+  <si>
+    <t>ENERGY</t>
+  </si>
+  <si>
+    <t>当前能量</t>
+  </si>
+  <si>
+    <t>AttributeValueFormat</t>
+  </si>
+  <si>
+    <t>属性值格式</t>
+  </si>
+  <si>
+    <t>VALUE</t>
+  </si>
+  <si>
+    <t>绝对值</t>
+  </si>
+  <si>
+    <t>RATE</t>
+  </si>
+  <si>
+    <t>比例值</t>
+  </si>
+  <si>
+    <t>表示万分比的整数值</t>
+  </si>
+  <si>
+    <t>AttributeType</t>
+  </si>
+  <si>
+    <t>属性值类型</t>
+  </si>
+  <si>
+    <t>MAX_LIFE</t>
+  </si>
+  <si>
+    <t>最大生命值</t>
+  </si>
+  <si>
+    <t>SPEED</t>
+  </si>
+  <si>
+    <t>速度</t>
+  </si>
+  <si>
+    <t>FIRE_COOLDOWN_RATE</t>
+  </si>
+  <si>
+    <t>开火间隔修正比例</t>
+  </si>
+  <si>
+    <t>调整两轮开火之间的等待时间</t>
+  </si>
+  <si>
+    <t>SHOT_INTERVAL_RATE</t>
+  </si>
+  <si>
+    <t>发射间隔修正比例</t>
+  </si>
+  <si>
+    <t>调整同一轮内相邻子弹的发射间隔</t>
+  </si>
+  <si>
+    <t>SHOOT_NUM</t>
+  </si>
+  <si>
+    <t>子弹发射数</t>
+  </si>
+  <si>
+    <t>AircraftSizeType</t>
+  </si>
+  <si>
+    <t>飞机体型</t>
+  </si>
+  <si>
+    <t>SMALL</t>
+  </si>
+  <si>
+    <t>小型</t>
+  </si>
+  <si>
+    <t>MEDIUM</t>
+  </si>
+  <si>
+    <t>中型</t>
+  </si>
+  <si>
+    <t>LARGE</t>
+  </si>
+  <si>
+    <t>大型</t>
+  </si>
+  <si>
+    <t>GIANT</t>
+  </si>
+  <si>
+    <t>巨型</t>
+  </si>
+  <si>
+    <t>AircraftFireSize</t>
+  </si>
+  <si>
+    <t>着火规模</t>
+  </si>
+  <si>
+    <t>小</t>
+  </si>
+  <si>
+    <t>中</t>
+  </si>
+  <si>
+    <t>大</t>
   </si>
 </sst>
 </file>
@@ -1006,6 +1129,15 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right style="thin">
         <color rgb="FF7F7F7F"/>
@@ -1048,10 +1180,10 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left/>
+      <right style="thin">
         <color auto="1"/>
-      </left>
-      <right/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -1074,15 +1206,6 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -1329,7 +1452,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1385,44 +1508,80 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1431,61 +1590,16 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1958,7 +2072,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L82"/>
+  <dimension ref="A1:L102"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="2" customWidth="1"/>
@@ -1969,7 +2083,7 @@
     <col min="6" max="6" width="22.125" style="2" customWidth="1"/>
     <col min="7" max="7" width="5.25" style="2" customWidth="1"/>
     <col min="8" max="8" width="26.5" style="2" customWidth="1"/>
-    <col min="9" max="9" width="9.75" style="2" customWidth="1"/>
+    <col min="9" max="9" width="17.125" style="2" customWidth="1"/>
     <col min="10" max="10" width="6.125" style="2" customWidth="1"/>
     <col min="11" max="11" width="35.875" style="2" customWidth="1"/>
     <col min="12" max="16384" width="9" style="2" customWidth="1"/>
@@ -2000,10 +2114,10 @@
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="3" t="s">
@@ -2085,7 +2199,7 @@
       <c r="J5" s="7">
         <v>1</v>
       </c>
-      <c r="K5" s="20"/>
+      <c r="K5" s="21"/>
     </row>
     <row r="6" spans="2:11">
       <c r="B6" s="8"/>
@@ -2103,7 +2217,7 @@
       <c r="J6" s="2">
         <v>2</v>
       </c>
-      <c r="K6" s="21"/>
+      <c r="K6" s="22"/>
     </row>
     <row r="7" spans="2:11">
       <c r="B7" s="8"/>
@@ -2121,7 +2235,7 @@
       <c r="J7" s="2">
         <v>3</v>
       </c>
-      <c r="K7" s="21"/>
+      <c r="K7" s="22"/>
     </row>
     <row r="8" spans="2:11">
       <c r="B8" s="9"/>
@@ -2139,7 +2253,7 @@
       <c r="J8" s="10">
         <v>4</v>
       </c>
-      <c r="K8" s="22"/>
+      <c r="K8" s="23"/>
     </row>
     <row r="10" spans="2:11">
       <c r="B10" s="6" t="s">
@@ -2165,7 +2279,7 @@
       <c r="J10" s="7">
         <v>1</v>
       </c>
-      <c r="K10" s="20"/>
+      <c r="K10" s="21"/>
     </row>
     <row r="11" spans="2:11">
       <c r="B11" s="8"/>
@@ -2183,7 +2297,7 @@
       <c r="J11" s="2">
         <v>2</v>
       </c>
-      <c r="K11" s="21"/>
+      <c r="K11" s="22"/>
     </row>
     <row r="12" spans="2:11">
       <c r="B12" s="8"/>
@@ -2201,7 +2315,7 @@
       <c r="J12" s="2">
         <v>3</v>
       </c>
-      <c r="K12" s="21"/>
+      <c r="K12" s="22"/>
     </row>
     <row r="13" spans="2:11">
       <c r="B13" s="9"/>
@@ -2219,7 +2333,7 @@
       <c r="J13" s="10">
         <v>4</v>
       </c>
-      <c r="K13" s="22"/>
+      <c r="K13" s="23"/>
     </row>
     <row r="15" spans="2:11">
       <c r="B15" s="6" t="s">
@@ -2245,7 +2359,7 @@
       <c r="J15" s="7">
         <v>1</v>
       </c>
-      <c r="K15" s="20"/>
+      <c r="K15" s="21"/>
     </row>
     <row r="16" spans="2:11">
       <c r="B16" s="8"/>
@@ -2263,7 +2377,7 @@
       <c r="J16" s="2">
         <v>2</v>
       </c>
-      <c r="K16" s="21"/>
+      <c r="K16" s="22"/>
     </row>
     <row r="17" spans="2:11">
       <c r="B17" s="8"/>
@@ -2281,7 +2395,7 @@
       <c r="J17" s="2">
         <v>3</v>
       </c>
-      <c r="K17" s="21"/>
+      <c r="K17" s="22"/>
     </row>
     <row r="18" spans="2:11">
       <c r="B18" s="8"/>
@@ -2299,7 +2413,7 @@
       <c r="J18" s="2">
         <v>4</v>
       </c>
-      <c r="K18" s="21"/>
+      <c r="K18" s="22"/>
     </row>
     <row r="19" spans="2:11">
       <c r="B19" s="8"/>
@@ -2317,7 +2431,7 @@
       <c r="J19" s="2">
         <v>5</v>
       </c>
-      <c r="K19" s="21"/>
+      <c r="K19" s="22"/>
     </row>
     <row r="20" spans="2:11">
       <c r="B20" s="8"/>
@@ -2335,7 +2449,7 @@
       <c r="J20" s="2">
         <v>6</v>
       </c>
-      <c r="K20" s="21"/>
+      <c r="K20" s="22"/>
     </row>
     <row r="21" spans="2:11">
       <c r="B21" s="8"/>
@@ -2353,7 +2467,7 @@
       <c r="J21" s="2">
         <v>7</v>
       </c>
-      <c r="K21" s="21"/>
+      <c r="K21" s="22"/>
     </row>
     <row r="22" spans="2:11">
       <c r="B22" s="8"/>
@@ -2371,7 +2485,7 @@
       <c r="J22" s="2">
         <v>8</v>
       </c>
-      <c r="K22" s="21"/>
+      <c r="K22" s="22"/>
     </row>
     <row r="23" spans="2:11">
       <c r="B23" s="8"/>
@@ -2389,7 +2503,7 @@
       <c r="J23" s="2">
         <v>9</v>
       </c>
-      <c r="K23" s="21"/>
+      <c r="K23" s="22"/>
     </row>
     <row r="24" spans="2:11">
       <c r="B24" s="8"/>
@@ -2407,7 +2521,7 @@
       <c r="J24" s="2">
         <v>10</v>
       </c>
-      <c r="K24" s="21"/>
+      <c r="K24" s="22"/>
     </row>
     <row r="25" spans="2:11">
       <c r="B25" s="8"/>
@@ -2425,7 +2539,7 @@
       <c r="J25" s="2">
         <v>11</v>
       </c>
-      <c r="K25" s="21"/>
+      <c r="K25" s="22"/>
     </row>
     <row r="26" spans="2:11">
       <c r="B26" s="9"/>
@@ -2443,7 +2557,7 @@
       <c r="J26" s="10">
         <v>12</v>
       </c>
-      <c r="K26" s="22"/>
+      <c r="K26" s="23"/>
     </row>
     <row r="28" spans="2:11">
       <c r="B28" s="6" t="s">
@@ -2469,7 +2583,7 @@
       <c r="J28" s="7">
         <v>0</v>
       </c>
-      <c r="K28" s="20"/>
+      <c r="K28" s="21"/>
     </row>
     <row r="29" spans="2:11">
       <c r="B29" s="9"/>
@@ -2487,7 +2601,7 @@
       <c r="J29" s="10">
         <v>1</v>
       </c>
-      <c r="K29" s="22"/>
+      <c r="K29" s="23"/>
     </row>
     <row r="31" spans="2:11">
       <c r="B31" s="6" t="s">
@@ -2513,7 +2627,7 @@
       <c r="J31" s="7">
         <v>1</v>
       </c>
-      <c r="K31" s="20"/>
+      <c r="K31" s="21"/>
     </row>
     <row r="32" spans="2:11">
       <c r="B32" s="8"/>
@@ -2531,7 +2645,7 @@
       <c r="J32" s="2">
         <v>2</v>
       </c>
-      <c r="K32" s="21"/>
+      <c r="K32" s="22"/>
     </row>
     <row r="33" spans="2:11">
       <c r="B33" s="9"/>
@@ -2549,7 +2663,7 @@
       <c r="J33" s="10">
         <v>3</v>
       </c>
-      <c r="K33" s="22"/>
+      <c r="K33" s="23"/>
     </row>
     <row r="35" spans="2:11">
       <c r="B35" s="6" t="s">
@@ -2575,7 +2689,7 @@
       <c r="J35" s="7">
         <v>1</v>
       </c>
-      <c r="K35" s="20"/>
+      <c r="K35" s="21"/>
     </row>
     <row r="36" spans="2:11">
       <c r="B36" s="8"/>
@@ -2593,7 +2707,7 @@
       <c r="J36" s="2">
         <v>2</v>
       </c>
-      <c r="K36" s="21"/>
+      <c r="K36" s="22"/>
     </row>
     <row r="37" spans="2:11">
       <c r="B37" s="9"/>
@@ -2611,7 +2725,7 @@
       <c r="J37" s="10">
         <v>3</v>
       </c>
-      <c r="K37" s="22"/>
+      <c r="K37" s="23"/>
     </row>
     <row r="39" spans="1:12">
       <c r="A39" s="11"/>
@@ -2638,7 +2752,7 @@
       <c r="J39" s="13">
         <v>0</v>
       </c>
-      <c r="K39" s="23"/>
+      <c r="K39" s="24"/>
       <c r="L39" s="11"/>
     </row>
     <row r="40" spans="1:12">
@@ -2658,7 +2772,7 @@
       <c r="J40" s="11">
         <v>1</v>
       </c>
-      <c r="K40" s="24"/>
+      <c r="K40" s="25"/>
       <c r="L40" s="11"/>
     </row>
     <row r="41" spans="1:12">
@@ -2678,22 +2792,22 @@
       <c r="J41" s="16">
         <v>2</v>
       </c>
-      <c r="K41" s="25"/>
+      <c r="K41" s="26"/>
       <c r="L41" s="11"/>
     </row>
     <row r="42" spans="1:12">
-      <c r="A42" s="11"/>
-      <c r="B42" s="11"/>
-      <c r="C42" s="11"/>
-      <c r="D42" s="11"/>
-      <c r="E42" s="11"/>
-      <c r="F42" s="11"/>
-      <c r="G42" s="11"/>
-      <c r="H42" s="11"/>
-      <c r="I42" s="11"/>
-      <c r="J42" s="11"/>
-      <c r="K42" s="11"/>
-      <c r="L42" s="11"/>
+      <c r="A42"/>
+      <c r="B42"/>
+      <c r="C42"/>
+      <c r="D42"/>
+      <c r="E42"/>
+      <c r="F42"/>
+      <c r="G42"/>
+      <c r="H42"/>
+      <c r="I42"/>
+      <c r="J42"/>
+      <c r="K42"/>
+      <c r="L42"/>
     </row>
     <row r="43" spans="1:12">
       <c r="A43" s="11"/>
@@ -2720,7 +2834,7 @@
       <c r="J43" s="13">
         <v>0</v>
       </c>
-      <c r="K43" s="23"/>
+      <c r="K43" s="24"/>
       <c r="L43" s="11"/>
     </row>
     <row r="44" spans="1:12">
@@ -2740,7 +2854,7 @@
       <c r="J44" s="11">
         <v>2</v>
       </c>
-      <c r="K44" s="24"/>
+      <c r="K44" s="25"/>
       <c r="L44" s="11"/>
     </row>
     <row r="45" spans="1:12">
@@ -2760,7 +2874,7 @@
       <c r="J45" s="16">
         <v>3</v>
       </c>
-      <c r="K45" s="25"/>
+      <c r="K45" s="26"/>
       <c r="L45" s="11"/>
     </row>
     <row r="47" spans="1:12">
@@ -2788,7 +2902,7 @@
       <c r="J47" s="13">
         <v>0</v>
       </c>
-      <c r="K47" s="23"/>
+      <c r="K47" s="24"/>
       <c r="L47" s="11"/>
     </row>
     <row r="48" spans="1:12">
@@ -2808,201 +2922,207 @@
       <c r="J48" s="16">
         <v>1</v>
       </c>
-      <c r="K48" s="25"/>
+      <c r="K48" s="26"/>
       <c r="L48" s="11"/>
     </row>
     <row r="49" spans="1:12">
-      <c r="A49" s="11"/>
-      <c r="B49" s="11"/>
-      <c r="C49" s="11"/>
-      <c r="D49" s="11"/>
-      <c r="E49" s="11"/>
-      <c r="F49" s="11"/>
-      <c r="G49" s="11"/>
-      <c r="H49" s="11"/>
-      <c r="I49" s="11"/>
-      <c r="J49" s="11"/>
-      <c r="K49" s="11"/>
-      <c r="L49" s="11"/>
+      <c r="A49"/>
+      <c r="B49"/>
+      <c r="C49"/>
+      <c r="D49"/>
+      <c r="E49"/>
+      <c r="F49"/>
+      <c r="G49"/>
+      <c r="H49"/>
+      <c r="I49"/>
+      <c r="J49"/>
+      <c r="K49"/>
+      <c r="L49"/>
     </row>
     <row r="50" spans="1:12">
       <c r="A50" s="11"/>
-      <c r="B50" s="11"/>
-      <c r="C50" s="11"/>
-      <c r="D50" s="11"/>
-      <c r="E50" s="11"/>
-      <c r="F50" s="11"/>
-      <c r="G50" s="11"/>
-      <c r="H50" s="11"/>
-      <c r="I50" s="11"/>
-      <c r="J50" s="11"/>
-      <c r="K50" s="11"/>
+      <c r="B50" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="C50" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="D50" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E50" s="13"/>
+      <c r="F50" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="G50" s="13"/>
+      <c r="H50" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="I50" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="J50" s="13">
+        <v>0</v>
+      </c>
+      <c r="K50" s="24" t="s">
+        <v>111</v>
+      </c>
       <c r="L50" s="11"/>
     </row>
     <row r="51" spans="1:12">
       <c r="A51" s="11"/>
-      <c r="B51" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="C51" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="D51" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E51" s="13"/>
-      <c r="F51" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="G51" s="13"/>
-      <c r="H51" s="13" t="s">
-        <v>109</v>
-      </c>
-      <c r="I51" s="13" t="s">
-        <v>110</v>
-      </c>
-      <c r="J51" s="13">
-        <v>0</v>
-      </c>
-      <c r="K51" s="23" t="s">
-        <v>111</v>
+      <c r="B51" s="14"/>
+      <c r="C51" s="11"/>
+      <c r="D51" s="11"/>
+      <c r="E51" s="11"/>
+      <c r="F51" s="11"/>
+      <c r="G51" s="11"/>
+      <c r="H51" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="I51" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="J51" s="11">
+        <v>1</v>
+      </c>
+      <c r="K51" s="25" t="s">
+        <v>114</v>
       </c>
       <c r="L51" s="11"/>
     </row>
     <row r="52" spans="1:12">
       <c r="A52" s="11"/>
-      <c r="B52" s="14"/>
-      <c r="C52" s="11"/>
-      <c r="D52" s="11"/>
-      <c r="E52" s="11"/>
-      <c r="F52" s="11"/>
-      <c r="G52" s="11"/>
-      <c r="H52" s="11" t="s">
-        <v>112</v>
-      </c>
-      <c r="I52" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="J52" s="11">
-        <v>1</v>
-      </c>
-      <c r="K52" s="24" t="s">
-        <v>114</v>
+      <c r="B52" s="15"/>
+      <c r="C52" s="16"/>
+      <c r="D52" s="16"/>
+      <c r="E52" s="16"/>
+      <c r="F52" s="16"/>
+      <c r="G52" s="16"/>
+      <c r="H52" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="I52" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="J52" s="16">
+        <v>2</v>
+      </c>
+      <c r="K52" s="26" t="s">
+        <v>117</v>
       </c>
       <c r="L52" s="11"/>
     </row>
-    <row r="53" spans="1:12">
-      <c r="A53" s="11"/>
-      <c r="B53" s="15"/>
-      <c r="C53" s="16"/>
-      <c r="D53" s="16"/>
-      <c r="E53" s="16"/>
-      <c r="F53" s="16"/>
-      <c r="G53" s="16"/>
-      <c r="H53" s="16" t="s">
-        <v>115</v>
-      </c>
-      <c r="I53" s="16" t="s">
-        <v>116</v>
-      </c>
-      <c r="J53" s="16">
-        <v>2</v>
-      </c>
-      <c r="K53" s="25" t="s">
-        <v>117</v>
-      </c>
-      <c r="L53" s="11"/>
+    <row r="54" spans="1:12">
+      <c r="A54" s="11"/>
+      <c r="B54" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="C54" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="D54" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E54" s="13"/>
+      <c r="F54" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="G54" s="13"/>
+      <c r="H54" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="I54" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="J54" s="13">
+        <v>0</v>
+      </c>
+      <c r="K54" s="24"/>
+      <c r="L54" s="11"/>
     </row>
     <row r="55" spans="1:12">
       <c r="A55" s="11"/>
-      <c r="B55" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="C55" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="D55" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E55" s="13"/>
-      <c r="F55" s="13" t="s">
-        <v>119</v>
-      </c>
-      <c r="G55" s="13"/>
-      <c r="H55" s="13" t="s">
-        <v>120</v>
-      </c>
-      <c r="I55" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="J55" s="13">
-        <v>0</v>
-      </c>
-      <c r="K55" s="23"/>
+      <c r="B55" s="15"/>
+      <c r="C55" s="16"/>
+      <c r="D55" s="16"/>
+      <c r="E55" s="16"/>
+      <c r="F55" s="16"/>
+      <c r="G55" s="16"/>
+      <c r="H55" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="I55" s="16" t="s">
+        <v>123</v>
+      </c>
+      <c r="J55" s="16">
+        <v>1</v>
+      </c>
+      <c r="K55" s="26"/>
       <c r="L55" s="11"/>
     </row>
     <row r="56" spans="1:12">
-      <c r="A56" s="11"/>
-      <c r="B56" s="15"/>
-      <c r="C56" s="16"/>
-      <c r="D56" s="16"/>
-      <c r="E56" s="16"/>
-      <c r="F56" s="16"/>
-      <c r="G56" s="16"/>
-      <c r="H56" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="I56" s="16" t="s">
-        <v>123</v>
-      </c>
-      <c r="J56" s="16">
-        <v>1</v>
-      </c>
-      <c r="K56" s="25"/>
-      <c r="L56" s="11"/>
+      <c r="A56"/>
+      <c r="B56"/>
+      <c r="C56"/>
+      <c r="D56"/>
+      <c r="E56"/>
+      <c r="F56"/>
+      <c r="G56"/>
+      <c r="H56"/>
+      <c r="I56"/>
+      <c r="J56"/>
+      <c r="K56"/>
+      <c r="L56"/>
     </row>
     <row r="57" spans="1:12">
       <c r="A57" s="11"/>
-      <c r="B57" s="11"/>
-      <c r="C57" s="11"/>
-      <c r="D57" s="11"/>
-      <c r="E57" s="11"/>
-      <c r="F57" s="11"/>
-      <c r="G57" s="11"/>
-      <c r="H57" s="11"/>
-      <c r="I57" s="11"/>
-      <c r="J57" s="11"/>
-      <c r="K57" s="11"/>
+      <c r="B57" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="C57" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="D57" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E57" s="13"/>
+      <c r="F57" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="G57" s="13"/>
+      <c r="H57" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="I57" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="J57" s="13">
+        <v>0</v>
+      </c>
+      <c r="K57" s="24" t="s">
+        <v>128</v>
+      </c>
       <c r="L57" s="11"/>
     </row>
     <row r="58" spans="1:12">
       <c r="A58" s="11"/>
-      <c r="B58" s="12" t="s">
-        <v>124</v>
-      </c>
-      <c r="C58" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="D58" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E58" s="13"/>
-      <c r="F58" s="13" t="s">
-        <v>125</v>
-      </c>
-      <c r="G58" s="13"/>
-      <c r="H58" s="13" t="s">
-        <v>126</v>
-      </c>
-      <c r="I58" s="13" t="s">
-        <v>127</v>
-      </c>
-      <c r="J58" s="13">
-        <v>0</v>
-      </c>
-      <c r="K58" s="23" t="s">
-        <v>128</v>
-      </c>
+      <c r="B58" s="14"/>
+      <c r="C58" s="11"/>
+      <c r="D58" s="11"/>
+      <c r="E58" s="11"/>
+      <c r="F58" s="11"/>
+      <c r="G58" s="11"/>
+      <c r="H58" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="I58" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="J58" s="11">
+        <v>1</v>
+      </c>
+      <c r="K58" s="25"/>
       <c r="L58" s="11"/>
     </row>
     <row r="59" spans="1:12">
@@ -3014,15 +3134,15 @@
       <c r="F59" s="11"/>
       <c r="G59" s="11"/>
       <c r="H59" s="11" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="I59" s="11" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="J59" s="11">
-        <v>1</v>
-      </c>
-      <c r="K59" s="24"/>
+        <v>2</v>
+      </c>
+      <c r="K59" s="25"/>
       <c r="L59" s="11"/>
     </row>
     <row r="60" spans="1:12">
@@ -3034,386 +3154,732 @@
       <c r="F60" s="11"/>
       <c r="G60" s="11"/>
       <c r="H60" s="11" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="I60" s="11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="J60" s="11">
-        <v>2</v>
-      </c>
-      <c r="K60" s="24"/>
+        <v>3</v>
+      </c>
+      <c r="K60" s="25"/>
       <c r="L60" s="11"/>
     </row>
     <row r="61" spans="1:12">
       <c r="A61" s="11"/>
-      <c r="B61" s="14"/>
-      <c r="C61" s="11"/>
-      <c r="D61" s="11"/>
-      <c r="E61" s="11"/>
-      <c r="F61" s="11"/>
-      <c r="G61" s="11"/>
-      <c r="H61" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="I61" s="11" t="s">
-        <v>134</v>
-      </c>
-      <c r="J61" s="11">
+      <c r="B61" s="15"/>
+      <c r="C61" s="16"/>
+      <c r="D61" s="16"/>
+      <c r="E61" s="16"/>
+      <c r="F61" s="16"/>
+      <c r="G61" s="16"/>
+      <c r="H61" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="I61" s="16" t="s">
+        <v>136</v>
+      </c>
+      <c r="J61" s="16">
+        <v>4</v>
+      </c>
+      <c r="K61" s="26"/>
+      <c r="L61" s="11"/>
+    </row>
+    <row r="63" spans="2:11">
+      <c r="B63" s="17" t="s">
+        <v>137</v>
+      </c>
+      <c r="C63" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="D63" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="E63" s="18"/>
+      <c r="F63" s="18" t="s">
+        <v>138</v>
+      </c>
+      <c r="G63" s="18"/>
+      <c r="H63" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="I63" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="J63" s="18">
+        <v>0</v>
+      </c>
+      <c r="K63" s="27"/>
+    </row>
+    <row r="64" spans="2:11">
+      <c r="B64" s="19"/>
+      <c r="H64" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="I64" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="J64" s="2">
+        <v>1</v>
+      </c>
+      <c r="K64" s="28"/>
+    </row>
+    <row r="65" spans="2:11">
+      <c r="B65" s="19"/>
+      <c r="H65" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="I65" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="J65" s="2">
+        <v>2</v>
+      </c>
+      <c r="K65" s="28"/>
+    </row>
+    <row r="66" spans="2:11">
+      <c r="B66" s="19"/>
+      <c r="H66" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="I66" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="J66" s="2">
         <v>3</v>
       </c>
-      <c r="K61" s="24"/>
-      <c r="L61" s="11"/>
-    </row>
-    <row r="62" spans="1:12">
-      <c r="A62" s="11"/>
-      <c r="B62" s="15"/>
-      <c r="C62" s="16"/>
-      <c r="D62" s="16"/>
-      <c r="E62" s="16"/>
-      <c r="F62" s="16"/>
-      <c r="G62" s="16"/>
-      <c r="H62" s="16" t="s">
-        <v>135</v>
-      </c>
-      <c r="I62" s="16" t="s">
-        <v>136</v>
-      </c>
-      <c r="J62" s="16">
+      <c r="K66" s="28"/>
+    </row>
+    <row r="67" spans="2:11">
+      <c r="B67" s="19"/>
+      <c r="H67" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="I67" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="J67" s="2">
         <v>4</v>
       </c>
-      <c r="K62" s="25"/>
-      <c r="L62" s="11"/>
-    </row>
-    <row r="64" spans="2:11">
-      <c r="B64" s="17" t="s">
-        <v>137</v>
-      </c>
-      <c r="C64" s="18" t="b">
+      <c r="K67" s="28"/>
+    </row>
+    <row r="68" spans="2:11">
+      <c r="B68" s="29"/>
+      <c r="C68" s="30"/>
+      <c r="D68" s="30"/>
+      <c r="E68" s="30"/>
+      <c r="F68" s="30"/>
+      <c r="G68" s="30"/>
+      <c r="H68" s="30" t="s">
+        <v>149</v>
+      </c>
+      <c r="I68" s="30" t="s">
+        <v>150</v>
+      </c>
+      <c r="J68" s="30">
+        <v>5</v>
+      </c>
+      <c r="K68" s="44"/>
+    </row>
+    <row r="69" spans="1:12">
+      <c r="A69"/>
+      <c r="B69"/>
+      <c r="C69"/>
+      <c r="D69"/>
+      <c r="E69"/>
+      <c r="F69"/>
+      <c r="G69"/>
+      <c r="H69"/>
+      <c r="I69"/>
+      <c r="J69"/>
+      <c r="K69"/>
+      <c r="L69"/>
+    </row>
+    <row r="70" spans="1:12">
+      <c r="A70" s="31"/>
+      <c r="B70" s="32" t="s">
+        <v>151</v>
+      </c>
+      <c r="C70" s="33" t="b">
         <v>0</v>
       </c>
-      <c r="D64" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="E64" s="18"/>
-      <c r="F64" s="18" t="s">
-        <v>138</v>
-      </c>
-      <c r="G64" s="18"/>
-      <c r="H64" s="18" t="s">
-        <v>139</v>
-      </c>
-      <c r="I64" s="18" t="s">
-        <v>140</v>
-      </c>
-      <c r="J64" s="18">
+      <c r="D70" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="E70" s="33"/>
+      <c r="F70" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="G70" s="33"/>
+      <c r="H70" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="I70" s="33" t="s">
+        <v>154</v>
+      </c>
+      <c r="J70" s="33">
         <v>0</v>
       </c>
-      <c r="K64" s="26"/>
-    </row>
-    <row r="65" spans="2:11">
-      <c r="B65" s="27"/>
-      <c r="H65" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="I65" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="J65" s="2">
-        <v>1</v>
-      </c>
-      <c r="K65" s="45"/>
-    </row>
-    <row r="66" spans="2:11">
-      <c r="B66" s="27"/>
-      <c r="H66" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="I66" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="J66" s="2">
+      <c r="K70" s="45" t="s">
+        <v>155</v>
+      </c>
+      <c r="L70" s="31"/>
+    </row>
+    <row r="71" spans="1:12">
+      <c r="A71" s="31"/>
+      <c r="B71" s="34"/>
+      <c r="C71" s="31"/>
+      <c r="D71" s="31"/>
+      <c r="E71" s="31"/>
+      <c r="F71" s="31"/>
+      <c r="G71" s="31"/>
+      <c r="H71" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="I71" s="31" t="s">
+        <v>157</v>
+      </c>
+      <c r="J71" s="31">
+        <v>1</v>
+      </c>
+      <c r="K71" s="46" t="s">
+        <v>158</v>
+      </c>
+      <c r="L71" s="31"/>
+    </row>
+    <row r="72" spans="1:12">
+      <c r="A72" s="31"/>
+      <c r="B72" s="34"/>
+      <c r="C72" s="31"/>
+      <c r="D72" s="31"/>
+      <c r="E72" s="31"/>
+      <c r="F72" s="31"/>
+      <c r="G72" s="31"/>
+      <c r="H72" s="31" t="s">
+        <v>159</v>
+      </c>
+      <c r="I72" s="31" t="s">
+        <v>160</v>
+      </c>
+      <c r="J72" s="31">
         <v>2</v>
       </c>
-      <c r="K66" s="45"/>
-    </row>
-    <row r="67" spans="2:11">
-      <c r="B67" s="27"/>
-      <c r="H67" s="2" t="s">
+      <c r="K72" s="46" t="s">
+        <v>161</v>
+      </c>
+      <c r="L72" s="31"/>
+    </row>
+    <row r="73" spans="1:12">
+      <c r="A73" s="31"/>
+      <c r="B73" s="35"/>
+      <c r="C73" s="36"/>
+      <c r="D73" s="36"/>
+      <c r="E73" s="36"/>
+      <c r="F73" s="36"/>
+      <c r="G73" s="36"/>
+      <c r="H73" s="36" t="s">
+        <v>162</v>
+      </c>
+      <c r="I73" s="36" t="s">
+        <v>163</v>
+      </c>
+      <c r="J73" s="36">
+        <v>3</v>
+      </c>
+      <c r="K73" s="47" t="s">
+        <v>164</v>
+      </c>
+      <c r="L73" s="31"/>
+    </row>
+    <row r="75" spans="2:11">
+      <c r="B75" s="17" t="s">
+        <v>165</v>
+      </c>
+      <c r="C75" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="D75" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="E75" s="18"/>
+      <c r="F75" s="18" t="s">
+        <v>166</v>
+      </c>
+      <c r="G75" s="18"/>
+      <c r="H75" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="I75" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="J75" s="18">
+        <v>0</v>
+      </c>
+      <c r="K75" s="27"/>
+    </row>
+    <row r="76" spans="2:11">
+      <c r="B76" s="19"/>
+      <c r="C76" s="37"/>
+      <c r="D76" s="37"/>
+      <c r="E76" s="37"/>
+      <c r="F76" s="37"/>
+      <c r="G76" s="37"/>
+      <c r="H76" s="37" t="s">
+        <v>167</v>
+      </c>
+      <c r="I76" s="37" t="s">
+        <v>168</v>
+      </c>
+      <c r="J76" s="37">
+        <v>1</v>
+      </c>
+      <c r="K76" s="28"/>
+    </row>
+    <row r="77" spans="2:11">
+      <c r="B77" s="29"/>
+      <c r="C77" s="30"/>
+      <c r="D77" s="30"/>
+      <c r="E77" s="30"/>
+      <c r="F77" s="30"/>
+      <c r="G77" s="30"/>
+      <c r="H77" s="30" t="s">
+        <v>169</v>
+      </c>
+      <c r="I77" s="30" t="s">
+        <v>170</v>
+      </c>
+      <c r="J77" s="30">
+        <v>2</v>
+      </c>
+      <c r="K77" s="44"/>
+    </row>
+    <row r="79" spans="2:11">
+      <c r="B79" s="17" t="s">
+        <v>171</v>
+      </c>
+      <c r="C79" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="D79" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="E79" s="18"/>
+      <c r="F79" s="18" t="s">
+        <v>172</v>
+      </c>
+      <c r="G79" s="18"/>
+      <c r="H79" s="18" t="s">
+        <v>173</v>
+      </c>
+      <c r="I79" s="18" t="s">
+        <v>174</v>
+      </c>
+      <c r="J79" s="18">
+        <v>0</v>
+      </c>
+      <c r="K79" s="27"/>
+    </row>
+    <row r="80" spans="2:11">
+      <c r="B80" s="19"/>
+      <c r="C80" s="37"/>
+      <c r="D80" s="37"/>
+      <c r="E80" s="37"/>
+      <c r="F80" s="37"/>
+      <c r="G80" s="37"/>
+      <c r="H80" s="37" t="s">
+        <v>175</v>
+      </c>
+      <c r="I80" s="37" t="s">
+        <v>176</v>
+      </c>
+      <c r="J80" s="37">
+        <v>1</v>
+      </c>
+      <c r="K80" s="28"/>
+    </row>
+    <row r="81" spans="2:11">
+      <c r="B81" s="29"/>
+      <c r="C81" s="30"/>
+      <c r="D81" s="30"/>
+      <c r="E81" s="30"/>
+      <c r="F81" s="30"/>
+      <c r="G81" s="30"/>
+      <c r="H81" s="30" t="s">
+        <v>177</v>
+      </c>
+      <c r="I81" s="30" t="s">
+        <v>178</v>
+      </c>
+      <c r="J81" s="30">
+        <v>2</v>
+      </c>
+      <c r="K81" s="44"/>
+    </row>
+    <row r="83" spans="2:11">
+      <c r="B83" s="17" t="s">
+        <v>179</v>
+      </c>
+      <c r="C83" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="D83" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="E83" s="18"/>
+      <c r="F83" s="18" t="s">
+        <v>180</v>
+      </c>
+      <c r="G83" s="18"/>
+      <c r="H83" s="18" t="s">
         <v>145</v>
       </c>
-      <c r="I67" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="J67" s="2">
+      <c r="I83" s="18" t="s">
+        <v>181</v>
+      </c>
+      <c r="J83" s="18">
+        <v>1</v>
+      </c>
+      <c r="K83" s="27"/>
+    </row>
+    <row r="84" spans="2:11">
+      <c r="B84" s="29"/>
+      <c r="C84" s="30"/>
+      <c r="D84" s="30"/>
+      <c r="E84" s="30"/>
+      <c r="F84" s="30"/>
+      <c r="G84" s="30"/>
+      <c r="H84" s="30" t="s">
+        <v>182</v>
+      </c>
+      <c r="I84" s="30" t="s">
+        <v>183</v>
+      </c>
+      <c r="J84" s="30">
+        <v>2</v>
+      </c>
+      <c r="K84" s="44"/>
+    </row>
+    <row r="86" spans="2:11">
+      <c r="B86" s="17" t="s">
+        <v>184</v>
+      </c>
+      <c r="C86" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="D86" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="E86" s="18"/>
+      <c r="F86" s="18" t="s">
+        <v>185</v>
+      </c>
+      <c r="G86" s="18"/>
+      <c r="H86" s="18" t="s">
+        <v>186</v>
+      </c>
+      <c r="I86" s="18" t="s">
+        <v>187</v>
+      </c>
+      <c r="J86" s="18">
+        <v>0</v>
+      </c>
+      <c r="K86" s="27"/>
+    </row>
+    <row r="87" spans="2:11">
+      <c r="B87" s="29"/>
+      <c r="C87" s="30"/>
+      <c r="D87" s="30"/>
+      <c r="E87" s="30"/>
+      <c r="F87" s="30"/>
+      <c r="G87" s="30"/>
+      <c r="H87" s="30" t="s">
+        <v>188</v>
+      </c>
+      <c r="I87" s="30" t="s">
+        <v>189</v>
+      </c>
+      <c r="J87" s="30">
+        <v>1</v>
+      </c>
+      <c r="K87" s="44" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="89" spans="2:12">
+      <c r="B89" s="38" t="s">
+        <v>191</v>
+      </c>
+      <c r="C89" s="39" t="b">
+        <v>0</v>
+      </c>
+      <c r="D89" s="39" t="b">
+        <v>1</v>
+      </c>
+      <c r="E89" s="39"/>
+      <c r="F89" s="39" t="s">
+        <v>192</v>
+      </c>
+      <c r="G89" s="39"/>
+      <c r="H89" s="39" t="s">
+        <v>193</v>
+      </c>
+      <c r="I89" s="39" t="s">
+        <v>194</v>
+      </c>
+      <c r="J89" s="39">
+        <v>1</v>
+      </c>
+      <c r="K89" s="48"/>
+      <c r="L89" s="11"/>
+    </row>
+    <row r="90" spans="2:12">
+      <c r="B90" s="40"/>
+      <c r="H90" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="I90" s="11" t="s">
+        <v>196</v>
+      </c>
+      <c r="J90" s="11">
+        <v>2</v>
+      </c>
+      <c r="K90" s="49"/>
+      <c r="L90" s="11"/>
+    </row>
+    <row r="91" spans="2:12">
+      <c r="B91" s="40"/>
+      <c r="H91" s="11" t="s">
+        <v>197</v>
+      </c>
+      <c r="I91" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="J91" s="11">
         <v>3</v>
       </c>
-      <c r="K67" s="45"/>
-    </row>
-    <row r="68" spans="2:11">
-      <c r="B68" s="27"/>
-      <c r="H68" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="I68" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="J68" s="2">
+      <c r="K91" s="49" t="s">
+        <v>199</v>
+      </c>
+      <c r="L91" s="11"/>
+    </row>
+    <row r="92" spans="2:12">
+      <c r="B92" s="40"/>
+      <c r="H92" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="I92" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="J92" s="11">
         <v>4</v>
       </c>
-      <c r="K68" s="45"/>
-    </row>
-    <row r="69" spans="2:11">
-      <c r="B69" s="28"/>
-      <c r="C69" s="29"/>
-      <c r="D69" s="29"/>
-      <c r="E69" s="29"/>
-      <c r="F69" s="29"/>
-      <c r="G69" s="29"/>
-      <c r="H69" s="29" t="s">
-        <v>149</v>
-      </c>
-      <c r="I69" s="29" t="s">
-        <v>150</v>
-      </c>
-      <c r="J69" s="29">
+      <c r="K92" s="49" t="s">
+        <v>202</v>
+      </c>
+      <c r="L92" s="11"/>
+    </row>
+    <row r="93" spans="2:12">
+      <c r="B93" s="41"/>
+      <c r="C93" s="42"/>
+      <c r="D93" s="42"/>
+      <c r="E93" s="42"/>
+      <c r="F93" s="42"/>
+      <c r="G93" s="42"/>
+      <c r="H93" s="43" t="s">
+        <v>203</v>
+      </c>
+      <c r="I93" s="43" t="s">
+        <v>204</v>
+      </c>
+      <c r="J93" s="43">
         <v>5</v>
       </c>
-      <c r="K69" s="46"/>
-    </row>
-    <row r="70" spans="1:12">
-      <c r="A70" s="30"/>
-      <c r="B70" s="30"/>
-      <c r="C70" s="30"/>
-      <c r="D70" s="30"/>
-      <c r="E70" s="30"/>
-      <c r="F70" s="30"/>
-      <c r="G70" s="30"/>
-      <c r="H70" s="30"/>
-      <c r="I70" s="30"/>
-      <c r="J70" s="30"/>
-      <c r="K70" s="30"/>
-      <c r="L70" s="30"/>
-    </row>
-    <row r="71" spans="1:12">
-      <c r="A71" s="30"/>
-      <c r="B71" s="31" t="s">
-        <v>151</v>
-      </c>
-      <c r="C71" s="32" t="b">
+      <c r="K93" s="50"/>
+      <c r="L93" s="11"/>
+    </row>
+    <row r="94" spans="1:12">
+      <c r="A94"/>
+      <c r="B94"/>
+      <c r="C94"/>
+      <c r="D94"/>
+      <c r="E94"/>
+      <c r="F94"/>
+      <c r="G94"/>
+      <c r="H94"/>
+      <c r="I94"/>
+      <c r="J94"/>
+      <c r="K94"/>
+      <c r="L94"/>
+    </row>
+    <row r="95" spans="1:12">
+      <c r="A95"/>
+      <c r="B95" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="C95" s="7" t="b">
         <v>0</v>
       </c>
-      <c r="D71" s="32" t="b">
-        <v>1</v>
-      </c>
-      <c r="E71" s="32"/>
-      <c r="F71" s="32" t="s">
-        <v>152</v>
-      </c>
-      <c r="G71" s="32"/>
-      <c r="H71" s="32" t="s">
-        <v>153</v>
-      </c>
-      <c r="I71" s="32" t="s">
-        <v>154</v>
-      </c>
-      <c r="J71" s="32">
+      <c r="D95" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E95" s="7"/>
+      <c r="F95" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="G95" s="7"/>
+      <c r="H95" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="I95" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="J95" s="7">
+        <v>1</v>
+      </c>
+      <c r="K95" s="21"/>
+      <c r="L95"/>
+    </row>
+    <row r="96" spans="1:12">
+      <c r="A96"/>
+      <c r="B96" s="8"/>
+      <c r="C96" s="1"/>
+      <c r="D96" s="1"/>
+      <c r="E96" s="1"/>
+      <c r="F96" s="1"/>
+      <c r="G96" s="1"/>
+      <c r="H96" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="I96" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="J96" s="2">
+        <v>2</v>
+      </c>
+      <c r="K96" s="22"/>
+      <c r="L96"/>
+    </row>
+    <row r="97" spans="1:12">
+      <c r="A97"/>
+      <c r="B97" s="8"/>
+      <c r="C97" s="1"/>
+      <c r="D97" s="1"/>
+      <c r="E97" s="1"/>
+      <c r="F97" s="1"/>
+      <c r="G97" s="1"/>
+      <c r="H97" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="I97" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="J97" s="2">
+        <v>3</v>
+      </c>
+      <c r="K97" s="22"/>
+      <c r="L97"/>
+    </row>
+    <row r="98" spans="1:12">
+      <c r="A98"/>
+      <c r="B98" s="9"/>
+      <c r="C98" s="10"/>
+      <c r="D98" s="10"/>
+      <c r="E98" s="10"/>
+      <c r="F98" s="10"/>
+      <c r="G98" s="10"/>
+      <c r="H98" s="10" t="s">
+        <v>213</v>
+      </c>
+      <c r="I98" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="J98" s="10">
+        <v>4</v>
+      </c>
+      <c r="K98" s="23"/>
+      <c r="L98"/>
+    </row>
+    <row r="99" spans="1:12">
+      <c r="A99"/>
+      <c r="B99"/>
+      <c r="C99"/>
+      <c r="D99"/>
+      <c r="E99"/>
+      <c r="F99"/>
+      <c r="G99"/>
+      <c r="H99"/>
+      <c r="I99"/>
+      <c r="J99"/>
+      <c r="K99"/>
+      <c r="L99"/>
+    </row>
+    <row r="100" spans="1:12">
+      <c r="A100" s="11"/>
+      <c r="B100" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="C100" s="13" t="b">
         <v>0</v>
       </c>
-      <c r="K71" s="47" t="s">
-        <v>155</v>
-      </c>
-      <c r="L71" s="30"/>
-    </row>
-    <row r="72" spans="1:12">
-      <c r="A72" s="30"/>
-      <c r="B72" s="33"/>
-      <c r="C72" s="30"/>
-      <c r="D72" s="30"/>
-      <c r="E72" s="30"/>
-      <c r="F72" s="30"/>
-      <c r="G72" s="30"/>
-      <c r="H72" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="I72" s="30" t="s">
-        <v>157</v>
-      </c>
-      <c r="J72" s="30">
-        <v>1</v>
-      </c>
-      <c r="K72" s="48" t="s">
-        <v>158</v>
-      </c>
-      <c r="L72" s="30"/>
-    </row>
-    <row r="73" spans="1:12">
-      <c r="A73" s="30"/>
-      <c r="B73" s="33"/>
-      <c r="C73" s="30"/>
-      <c r="D73" s="30"/>
-      <c r="E73" s="30"/>
-      <c r="F73" s="30"/>
-      <c r="G73" s="30"/>
-      <c r="H73" s="30" t="s">
-        <v>159</v>
-      </c>
-      <c r="I73" s="30" t="s">
-        <v>160</v>
-      </c>
-      <c r="J73" s="30">
+      <c r="D100" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E100" s="13"/>
+      <c r="F100" s="13" t="s">
+        <v>216</v>
+      </c>
+      <c r="G100" s="13"/>
+      <c r="H100" s="13" t="s">
+        <v>207</v>
+      </c>
+      <c r="I100" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="J100" s="13">
+        <v>1</v>
+      </c>
+      <c r="K100" s="24"/>
+      <c r="L100" s="11"/>
+    </row>
+    <row r="101" spans="1:12">
+      <c r="A101" s="11"/>
+      <c r="B101" s="14"/>
+      <c r="C101" s="11"/>
+      <c r="D101" s="11"/>
+      <c r="E101" s="11"/>
+      <c r="F101" s="11"/>
+      <c r="G101" s="11"/>
+      <c r="H101" s="11" t="s">
+        <v>209</v>
+      </c>
+      <c r="I101" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="J101" s="11">
         <v>2</v>
       </c>
-      <c r="K73" s="48" t="s">
-        <v>161</v>
-      </c>
-      <c r="L73" s="30"/>
-    </row>
-    <row r="74" spans="1:12">
-      <c r="A74" s="30"/>
-      <c r="B74" s="34"/>
-      <c r="C74" s="35"/>
-      <c r="D74" s="35"/>
-      <c r="E74" s="35"/>
-      <c r="F74" s="35"/>
-      <c r="G74" s="35"/>
-      <c r="H74" s="35" t="s">
-        <v>162</v>
-      </c>
-      <c r="I74" s="35" t="s">
-        <v>163</v>
-      </c>
-      <c r="J74" s="35">
+      <c r="K101" s="25"/>
+      <c r="L101" s="11"/>
+    </row>
+    <row r="102" spans="1:12">
+      <c r="A102" s="11"/>
+      <c r="B102" s="15"/>
+      <c r="C102" s="16"/>
+      <c r="D102" s="16"/>
+      <c r="E102" s="16"/>
+      <c r="F102" s="16"/>
+      <c r="G102" s="16"/>
+      <c r="H102" s="16" t="s">
+        <v>211</v>
+      </c>
+      <c r="I102" s="16" t="s">
+        <v>219</v>
+      </c>
+      <c r="J102" s="16">
         <v>3</v>
       </c>
-      <c r="K74" s="49" t="s">
-        <v>164</v>
-      </c>
-      <c r="L74" s="30"/>
-    </row>
-    <row r="76" spans="2:11">
-      <c r="B76" s="17" t="s">
-        <v>165</v>
-      </c>
-      <c r="C76" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="D76" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="E76" s="18"/>
-      <c r="F76" s="18" t="s">
-        <v>166</v>
-      </c>
-      <c r="G76" s="18"/>
-      <c r="H76" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="I76" s="36" t="s">
-        <v>88</v>
-      </c>
-      <c r="J76" s="18">
-        <v>0</v>
-      </c>
-      <c r="K76" s="26"/>
-    </row>
-    <row r="77" spans="2:11">
-      <c r="B77" s="27"/>
-      <c r="C77" s="37"/>
-      <c r="D77" s="37"/>
-      <c r="E77" s="37"/>
-      <c r="F77" s="37"/>
-      <c r="G77" s="37"/>
-      <c r="H77" s="37" t="s">
-        <v>167</v>
-      </c>
-      <c r="I77" s="37" t="s">
-        <v>168</v>
-      </c>
-      <c r="J77" s="37">
-        <v>1</v>
-      </c>
-      <c r="K77" s="45"/>
-    </row>
-    <row r="78" spans="2:11">
-      <c r="B78" s="38"/>
-      <c r="C78" s="39"/>
-      <c r="D78" s="39"/>
-      <c r="E78" s="39"/>
-      <c r="F78" s="39"/>
-      <c r="G78" s="39"/>
-      <c r="H78" s="29" t="s">
-        <v>169</v>
-      </c>
-      <c r="I78" s="29" t="s">
-        <v>170</v>
-      </c>
-      <c r="J78" s="39">
-        <v>2</v>
-      </c>
-      <c r="K78" s="50"/>
-    </row>
-    <row r="80" spans="2:11">
-      <c r="B80" s="17" t="s">
-        <v>171</v>
-      </c>
-      <c r="C80" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="D80" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="E80" s="40"/>
-      <c r="F80" s="18" t="s">
-        <v>172</v>
-      </c>
-      <c r="G80" s="40"/>
-      <c r="H80" s="40" t="s">
-        <v>173</v>
-      </c>
-      <c r="I80" s="40" t="s">
-        <v>174</v>
-      </c>
-      <c r="J80" s="40">
-        <v>0</v>
-      </c>
-      <c r="K80" s="51"/>
-    </row>
-    <row r="81" spans="2:11">
-      <c r="B81" s="41"/>
-      <c r="C81" s="37"/>
-      <c r="D81" s="37"/>
-      <c r="E81" s="37"/>
-      <c r="F81" s="37"/>
-      <c r="G81" s="37"/>
-      <c r="H81" s="42" t="s">
-        <v>175</v>
-      </c>
-      <c r="I81" s="42" t="s">
-        <v>176</v>
-      </c>
-      <c r="J81" s="37">
-        <v>1</v>
-      </c>
-      <c r="K81" s="52"/>
-    </row>
-    <row r="82" spans="2:11">
-      <c r="B82" s="43"/>
-      <c r="C82" s="44"/>
-      <c r="D82" s="44"/>
-      <c r="E82" s="44"/>
-      <c r="F82" s="44"/>
-      <c r="G82" s="44"/>
-      <c r="H82" s="44" t="s">
-        <v>177</v>
-      </c>
-      <c r="I82" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="J82" s="44">
-        <v>2</v>
-      </c>
-      <c r="K82" s="53"/>
+      <c r="K102" s="26"/>
+      <c r="L102" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="1">
